--- a/research/traditional_assets/database/data/tunisia/tunisia_apparel.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_apparel.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,67 +588,79 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0174</v>
+        <v>0.00936</v>
       </c>
       <c r="E2">
-        <v>0.057</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="G2">
-        <v>0.02114312267657992</v>
+        <v>0.4465240641711229</v>
       </c>
       <c r="H2">
-        <v>0.02114312267657992</v>
+        <v>0.4465240641711229</v>
       </c>
       <c r="I2">
-        <v>-0.03917286245353159</v>
+        <v>0.113903743315508</v>
       </c>
       <c r="J2">
-        <v>-0.03698822204746925</v>
+        <v>0.0958646889442737</v>
       </c>
       <c r="K2">
-        <v>-2.124</v>
+        <v>0.372</v>
       </c>
       <c r="L2">
-        <v>-0.0986988847583643</v>
+        <v>0.1989304812834224</v>
       </c>
       <c r="M2">
-        <v>0.411</v>
+        <v>0.485</v>
       </c>
       <c r="N2">
-        <v>0.03357843137254902</v>
+        <v>0.07111436950146627</v>
       </c>
       <c r="O2">
-        <v>-0.1935028248587571</v>
+        <v>1.303763440860215</v>
       </c>
       <c r="P2">
-        <v>0.4</v>
+        <v>0.485</v>
       </c>
       <c r="Q2">
-        <v>0.03267973856209151</v>
+        <v>0.07111436950146627</v>
       </c>
       <c r="R2">
-        <v>-0.1883239171374765</v>
+        <v>1.303763440860215</v>
       </c>
       <c r="S2">
-        <v>0.01100000000000001</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.02676399026763993</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1.59</v>
+        <v>0.312</v>
       </c>
       <c r="V2">
-        <v>0.1299019607843137</v>
+        <v>0.04574780058651026</v>
+      </c>
+      <c r="W2">
+        <v>0.08691588785046728</v>
       </c>
       <c r="X2">
-        <v>0.118225641224969</v>
+        <v>0.1979159530919335</v>
+      </c>
+      <c r="Y2">
+        <v>-0.1110000652414663</v>
       </c>
       <c r="Z2">
-        <v>5.957918050941307</v>
+        <v>0.6951672862453531</v>
+      </c>
+      <c r="AA2">
+        <v>0.06664199566014567</v>
       </c>
       <c r="AB2">
-        <v>0.118225641224969</v>
+        <v>0.1979159530919335</v>
+      </c>
+      <c r="AC2">
+        <v>-0.1312739574317879</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -660,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-1.59</v>
+        <v>-0.312</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -669,28 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.1492957746478873</v>
+        <v>-0.04794099569760295</v>
       </c>
       <c r="AK2">
-        <v>-0.591078066914498</v>
+        <v>-0.09291244788564622</v>
       </c>
       <c r="AL2">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>1.52</v>
+        <v>-0.246</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
-      <c r="AO2">
-        <v>-0.4872832369942196</v>
-      </c>
       <c r="AP2">
-        <v>-1.512844909609895</v>
+        <v>-1.006451612903226</v>
       </c>
       <c r="AQ2">
-        <v>-0.5546052631578946</v>
+        <v>-0.8658536585365854</v>
       </c>
     </row>
     <row r="3">
@@ -710,79 +719,79 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0168</v>
+        <v>0.00936</v>
       </c>
       <c r="E3">
-        <v>0.057</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="G3">
-        <v>0.1166666666666667</v>
+        <v>0.4465240641711229</v>
       </c>
       <c r="H3">
-        <v>0.1166666666666667</v>
+        <v>0.4465240641711229</v>
       </c>
       <c r="I3">
-        <v>0.3162698412698413</v>
+        <v>0.113903743315508</v>
       </c>
       <c r="J3">
-        <v>0.2809935897435897</v>
+        <v>0.0958646889442737</v>
       </c>
       <c r="K3">
-        <v>0.926</v>
+        <v>0.372</v>
       </c>
       <c r="L3">
-        <v>0.3674603174603175</v>
+        <v>0.1989304812834224</v>
       </c>
       <c r="M3">
-        <v>0.388</v>
+        <v>0.485</v>
       </c>
       <c r="N3">
-        <v>0.05271739130434783</v>
+        <v>0.07111436950146627</v>
       </c>
       <c r="O3">
-        <v>0.4190064794816414</v>
+        <v>1.303763440860215</v>
       </c>
       <c r="P3">
-        <v>0.377</v>
+        <v>0.485</v>
       </c>
       <c r="Q3">
-        <v>0.05122282608695652</v>
+        <v>0.07111436950146627</v>
       </c>
       <c r="R3">
-        <v>0.4071274298056156</v>
+        <v>1.303763440860215</v>
       </c>
       <c r="S3">
-        <v>0.01100000000000001</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.02835051546391755</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.59</v>
+        <v>0.312</v>
       </c>
       <c r="V3">
-        <v>0.2160326086956522</v>
+        <v>0.04574780058651026</v>
       </c>
       <c r="W3">
-        <v>0.2220623501199041</v>
+        <v>0.08691588785046728</v>
       </c>
       <c r="X3">
-        <v>0.118225641224969</v>
+        <v>0.1979159530919335</v>
       </c>
       <c r="Y3">
-        <v>0.1038367088949351</v>
+        <v>-0.1110000652414663</v>
       </c>
       <c r="Z3">
-        <v>0.6976744186046512</v>
+        <v>0.6951672862453531</v>
       </c>
       <c r="AA3">
-        <v>0.1960420393559928</v>
+        <v>0.06664199566014567</v>
       </c>
       <c r="AB3">
-        <v>0.118225641224969</v>
+        <v>0.1979159530919335</v>
       </c>
       <c r="AC3">
-        <v>0.0778163981310239</v>
+        <v>-0.1312739574317879</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-1.59</v>
+        <v>-0.312</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,135 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.2755632582322357</v>
+        <v>-0.04794099569760295</v>
       </c>
       <c r="AK3">
-        <v>-0.591078066914498</v>
+        <v>-0.09291244788564622</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.21</v>
+        <v>-0.246</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1.786516853932584</v>
+        <v>-1.006451612903226</v>
       </c>
       <c r="AQ3">
-        <v>-3.795238095238096</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Societe Industrielle des Textiles S.A. (BVMT:SITEX)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Apparel</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.018</v>
-      </c>
-      <c r="G4">
-        <v>0.008473684210526316</v>
-      </c>
-      <c r="H4">
-        <v>0.008473684210526316</v>
-      </c>
-      <c r="I4">
-        <v>-0.08631578947368421</v>
-      </c>
-      <c r="J4">
-        <v>-0.08631578947368421</v>
-      </c>
-      <c r="K4">
-        <v>-3.05</v>
-      </c>
-      <c r="L4">
-        <v>-0.1605263157894737</v>
-      </c>
-      <c r="M4">
-        <v>0.023</v>
-      </c>
-      <c r="N4">
-        <v>0.004713114754098361</v>
-      </c>
-      <c r="O4">
-        <v>-0.007540983606557377</v>
-      </c>
-      <c r="P4">
-        <v>0.023</v>
-      </c>
-      <c r="Q4">
-        <v>0.004713114754098361</v>
-      </c>
-      <c r="R4">
-        <v>-0.007540983606557377</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0.118225641224969</v>
-      </c>
-      <c r="AB4">
-        <v>0.118225641224969</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>1.73</v>
-      </c>
-      <c r="AM4">
-        <v>1.73</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>-0.9479768786127167</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>-0.9479768786127167</v>
+        <v>-0.8658536585365854</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/tunisia/tunisia_apparel.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_apparel.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00936</v>
+        <v>-0.0219</v>
       </c>
       <c r="E2">
-        <v>-0.07099999999999999</v>
+        <v>-0.0751</v>
       </c>
       <c r="G2">
-        <v>0.4465240641711229</v>
+        <v>0.1364640883977901</v>
       </c>
       <c r="H2">
-        <v>0.4465240641711229</v>
+        <v>0.1364640883977901</v>
       </c>
       <c r="I2">
-        <v>0.113903743315508</v>
+        <v>0.1320441988950276</v>
       </c>
       <c r="J2">
-        <v>0.0958646889442737</v>
+        <v>0.1141258838048882</v>
       </c>
       <c r="K2">
-        <v>0.372</v>
+        <v>0.413</v>
       </c>
       <c r="L2">
-        <v>0.1989304812834224</v>
+        <v>0.2281767955801105</v>
       </c>
       <c r="M2">
-        <v>0.485</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="N2">
-        <v>0.07111436950146627</v>
+        <v>0.09346938775510205</v>
       </c>
       <c r="O2">
-        <v>1.303763440860215</v>
+        <v>1.663438256658596</v>
       </c>
       <c r="P2">
-        <v>0.485</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.07111436950146627</v>
+        <v>0.09346938775510205</v>
       </c>
       <c r="R2">
-        <v>1.303763440860215</v>
+        <v>1.663438256658596</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.312</v>
+        <v>0.412</v>
       </c>
       <c r="V2">
-        <v>0.04574780058651026</v>
+        <v>0.05605442176870748</v>
       </c>
       <c r="W2">
-        <v>0.08691588785046728</v>
+        <v>0.1125340599455041</v>
       </c>
       <c r="X2">
-        <v>0.1979159530919335</v>
+        <v>0.1762607994766319</v>
       </c>
       <c r="Y2">
-        <v>-0.1110000652414663</v>
+        <v>-0.06372673953112784</v>
       </c>
       <c r="Z2">
-        <v>0.6951672862453531</v>
+        <v>0.5390113162596784</v>
       </c>
       <c r="AA2">
-        <v>0.06664199566014567</v>
+        <v>0.06151514284897188</v>
       </c>
       <c r="AB2">
-        <v>0.1979159530919335</v>
+        <v>0.1762607994766319</v>
       </c>
       <c r="AC2">
-        <v>-0.1312739574317879</v>
+        <v>-0.11474565662766</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.312</v>
+        <v>-0.412</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,25 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.04794099569760295</v>
+        <v>-0.05938310752378207</v>
       </c>
       <c r="AK2">
-        <v>-0.09291244788564622</v>
+        <v>-0.12568639414277</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.246</v>
+        <v>-0.216</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-1.006451612903226</v>
+        <v>-1.30379746835443</v>
       </c>
       <c r="AQ2">
-        <v>-0.8658536585365854</v>
+        <v>-1.106481481481481</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00936</v>
+        <v>-0.0219</v>
       </c>
       <c r="E3">
-        <v>-0.07099999999999999</v>
+        <v>-0.0751</v>
       </c>
       <c r="G3">
-        <v>0.4465240641711229</v>
+        <v>0.1364640883977901</v>
       </c>
       <c r="H3">
-        <v>0.4465240641711229</v>
+        <v>0.1364640883977901</v>
       </c>
       <c r="I3">
-        <v>0.113903743315508</v>
+        <v>0.1320441988950276</v>
       </c>
       <c r="J3">
-        <v>0.0958646889442737</v>
+        <v>0.1141258838048882</v>
       </c>
       <c r="K3">
-        <v>0.372</v>
+        <v>0.413</v>
       </c>
       <c r="L3">
-        <v>0.1989304812834224</v>
+        <v>0.2281767955801105</v>
       </c>
       <c r="M3">
-        <v>0.485</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="N3">
-        <v>0.07111436950146627</v>
+        <v>0.09346938775510205</v>
       </c>
       <c r="O3">
-        <v>1.303763440860215</v>
+        <v>1.663438256658596</v>
       </c>
       <c r="P3">
-        <v>0.485</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.07111436950146627</v>
+        <v>0.09346938775510205</v>
       </c>
       <c r="R3">
-        <v>1.303763440860215</v>
+        <v>1.663438256658596</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.312</v>
+        <v>0.412</v>
       </c>
       <c r="V3">
-        <v>0.04574780058651026</v>
+        <v>0.05605442176870748</v>
       </c>
       <c r="W3">
-        <v>0.08691588785046728</v>
+        <v>0.1125340599455041</v>
       </c>
       <c r="X3">
-        <v>0.1979159530919335</v>
+        <v>0.1762607994766319</v>
       </c>
       <c r="Y3">
-        <v>-0.1110000652414663</v>
+        <v>-0.06372673953112784</v>
       </c>
       <c r="Z3">
-        <v>0.6951672862453531</v>
+        <v>0.5390113162596784</v>
       </c>
       <c r="AA3">
-        <v>0.06664199566014567</v>
+        <v>0.06151514284897188</v>
       </c>
       <c r="AB3">
-        <v>0.1979159530919335</v>
+        <v>0.1762607994766319</v>
       </c>
       <c r="AC3">
-        <v>-0.1312739574317879</v>
+        <v>-0.11474565662766</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.312</v>
+        <v>-0.412</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,25 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.04794099569760295</v>
+        <v>-0.05938310752378207</v>
       </c>
       <c r="AK3">
-        <v>-0.09291244788564622</v>
+        <v>-0.12568639414277</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.246</v>
+        <v>-0.216</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1.006451612903226</v>
+        <v>-1.30379746835443</v>
       </c>
       <c r="AQ3">
-        <v>-0.8658536585365854</v>
+        <v>-1.106481481481481</v>
       </c>
     </row>
   </sheetData>
